--- a/test/snap/styles.snap.xlsx
+++ b/test/snap/styles.snap.xlsx
@@ -52,7 +52,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <cols>
     <col min="1" max="1"/>
   </cols>
@@ -69,6 +69,16 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sized Row</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/test/snap/styles.snap.xlsx
+++ b/test/snap/styles.snap.xlsx
@@ -52,7 +52,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <cols>
     <col min="1" max="1"/>
   </cols>
@@ -69,16 +69,26 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="25" customHeight="1">
+    <row r="2" hidden="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sized Row</t>
+          <t>Hidden Row</t>
         </is>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
     </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sized Row</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/test/snap/styles.snap.xlsx
+++ b/test/snap/styles.snap.xlsx
@@ -36,16 +36,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border/>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="double"/>
+    </border>
   </borders>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf fontId="0" applyFont="1"/>
     <xf numFmtId="164" applyNumberFormat="1"/>
     <xf numFmtId="165" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" applyFont="1"/>
     <xf fontId="2"/>
     <xf fontId="0"/>
+    <xf fontId="0" borderId="1" applyBorder="1"/>
+    <xf fontId="0" borderId="2" applyBorder="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -85,7 +96,7 @@
           <t>Sized Row</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" s="6">
         <v>1</v>
       </c>
     </row>

--- a/test/snap/styles.snap.xlsx
+++ b/test/snap/styles.snap.xlsx
@@ -28,12 +28,22 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <bgColor rgb="FF9900"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -48,7 +58,7 @@
       <top style="double"/>
     </border>
   </borders>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf fontId="0" applyFont="1"/>
     <xf numFmtId="164" applyNumberFormat="1"/>
     <xf numFmtId="165" applyNumberFormat="1"/>
@@ -57,13 +67,15 @@
     <xf fontId="0"/>
     <xf fontId="0" borderId="1" applyBorder="1"/>
     <xf fontId="0" borderId="2" applyBorder="1"/>
+    <xf fontId="0" fillId="2" applyFill="1"/>
+    <xf fontId="0" fillId="3" applyFill="1"/>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <cols>
     <col min="1" max="1"/>
   </cols>
@@ -100,6 +112,16 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Filled</t>
+        </is>
+      </c>
+      <c r="B4" s="9">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/test/snap/styles.snap.xlsx
+++ b/test/snap/styles.snap.xlsx
@@ -19,9 +19,9 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
       <sz val="15"/>
@@ -37,12 +37,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <bgColor rgb="FF9900"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,6 +58,9 @@
       <top style="double"/>
     </border>
   </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
   <cellXfs count="10">
     <xf fontId="0" applyFont="1"/>
     <xf numFmtId="164" applyNumberFormat="1"/>
@@ -70,6 +73,9 @@
     <xf fontId="0" fillId="2" applyFill="1"/>
     <xf fontId="0" fillId="3" applyFill="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 

--- a/test/snap/styles.snap.xlsx
+++ b/test/snap/styles.snap.xlsx
@@ -19,9 +19,9 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b val="1"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
       <sz val="15"/>
@@ -37,12 +37,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <bgColor rgb="FF9900"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,18 +58,24 @@
       <top style="double"/>
     </border>
   </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
   <cellXfs count="10">
-    <xf fontId="0" applyFont="1"/>
-    <xf numFmtId="164" applyNumberFormat="1"/>
-    <xf numFmtId="165" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" applyFont="1"/>
-    <xf fontId="2"/>
-    <xf fontId="0"/>
-    <xf fontId="0" borderId="1" applyBorder="1"/>
-    <xf fontId="0" borderId="2" applyBorder="1"/>
-    <xf fontId="0" fillId="2" applyFill="1"/>
-    <xf fontId="0" fillId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" borderId="0" fillId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" borderId="0" fillId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" borderId="1" fillId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" borderId="2" fillId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" borderId="0" fillId="2" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" borderId="0" fillId="3" xfId="0" applyFill="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 

--- a/test/snap/styles.snap.xlsx
+++ b/test/snap/styles.snap.xlsx
@@ -63,7 +63,7 @@
     <xf numFmtId="164" applyNumberFormat="1"/>
     <xf numFmtId="165" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" applyFont="1"/>
-    <xf fontId="2"/>
+    <xf fontId="2" applyFont="1"/>
     <xf fontId="0"/>
     <xf fontId="0" borderId="1" applyBorder="1"/>
     <xf fontId="0" borderId="2" applyBorder="1"/>

--- a/test/snap/styles.snap.xlsx
+++ b/test/snap/styles.snap.xlsx
@@ -13,7 +13,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -25,6 +25,17 @@
     </font>
     <font>
       <sz val="15"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFCC0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="-0.25"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -46,7 +57,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border/>
     <border>
       <left style="thin"/>
@@ -57,11 +68,19 @@
     <border>
       <top style="double"/>
     </border>
+    <border>
+      <right style="medium">
+        <color rgb="FFCC0000"/>
+      </right>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf fontId="0" applyFont="1"/>
     <xf numFmtId="164" applyNumberFormat="1"/>
     <xf numFmtId="165" applyNumberFormat="1"/>
@@ -70,8 +89,11 @@
     <xf fontId="0"/>
     <xf fontId="0" borderId="1" applyBorder="1"/>
     <xf fontId="0" borderId="2" applyBorder="1"/>
+    <xf fontId="0" borderId="3" applyBorder="1"/>
     <xf fontId="0" fillId="2" applyFill="1"/>
     <xf fontId="0" fillId="3" applyFill="1"/>
+    <xf fontId="3" applyFont="1"/>
+    <xf fontId="4" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -81,7 +103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <cols>
     <col min="1" max="1"/>
   </cols>
@@ -119,13 +141,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Filled</t>
         </is>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="10">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Red bold</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Themed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Colored border</t>
+        </is>
       </c>
     </row>
   </sheetData>
